--- a/01-03-01/one-line-card-blank.xlsx
+++ b/01-03-01/one-line-card-blank.xlsx
@@ -526,7 +526,7 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>다음엔 이것부터 (가 → 매번 「매뉴얼에 반영했어?」까지 묻기 · 나 → 고칠 점을 모아 자세히 말하고 기준에 반영하기 · 다 → 잘 나오면 「스킬로 만들어 줘」)</t>
+          <t>다음엔 이것부터 (가 → 매번 「했어? 매뉴얼 반영했어?」까지 묻기 · 나 → 어디가 왜 별로인지 짚어서 말하고 기준에 반영하기 · 다 → 잘 나오면 「스킬로 만들어 줘」)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>처음 구간엔 새 직원 첫 달처럼 매번 「매뉴얼에 반영했어?」까지 물어요. 계속 고치는 건 실패가 아니라 키우는 중이에요</t>
+          <t>처음 구간엔 새 직원 처음처럼 매번 「했어? 매뉴얼 반영했어?」까지 물어요. 계속 고치는 건 실패가 아니라 키우는 중이에요</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>결과가 별로일 때 뭐가 틀렸는지는 말하지 않고 「이거 좀 바꿔 줘」만 하거나, AI·직원 탓을 하다 멈췄다</t>
+          <t>결과가 별로일 때 뭐가 틀렸는지는 말하지 않고 그냥 바꿔 달라고만 하거나, AI·직원 탓을 하다 멈췄다</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>고칠 점을 한 번에 모아 자세히 말해요. 실수가 나면 탓하지 말고 돌아보고 순서·기준에 반영해요</t>
+          <t>고칠 점은 어디가 왜 별로인지 짚어서 말해요. 실수가 나면 탓하지 말고 돌아보고 순서·기준에 반영해요</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -702,19 +702,12 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>아직 맡겨 본 적이 없으면, 설치나 결제만 해 두고 손을 놓은 일을 적어요. 그때 「어차피 매번 손이 갈 것 같아서」였다면 첫 번째(가)예요.</t>
+          <t>아직 맡겨 본 적이 없으시면, 결제나 설치만 해 두고 손 놓은 일을 적으셔도 돼요.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>가·나·다가 둘 이상 걸리면 가장 먼저 멈춘 쪽 하나만 골라요. 한 줄 카드는 지금 하나만 고치려고 쓰는 거예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>한 줄로 옮기기: 「나는 ( 일 )을 맡기다 ( 첫 번째 / 두 번째 / 세 번째 ) 공통점에서 멈추는 사람이다. 다음엔 ( 첫 걸음 )부터.」</t>
         </is>

--- a/01-03-01/one-line-card-blank.xlsx
+++ b/01-03-01/one-line-card-blank.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>처음 몇 번 고쳐 주다가 「이렇게 계속 손이 가면 의미 없다」 하고 멈췄다</t>
+          <t>처음 몇 번 고쳐 주다가 계속 이렇게 손이 가면 의미 없겠다 싶어 멈췄다</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">

--- a/01-03-01/one-line-card-blank.xlsx
+++ b/01-03-01/one-line-card-blank.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="한 줄 카드" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="가·나·다 읽는 법" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공통점 세 가지" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="칸 읽는 법" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -518,7 +518,7 @@
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>나는 어디서 멈췄나 (첫 번째 가 · 두 번째 나 · 세 번째 다)</t>
+          <t>나는 어디서 멈췄나 (첫 번째 · 두 번째 · 세 번째)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
@@ -526,7 +526,7 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>다음엔 이것부터 (가 → 매번 「했어? 매뉴얼 반영했어?」까지 묻기 · 나 → 어디가 왜 별로인지 짚어서 말하고 기준에 반영하기 · 다 → 잘 나오면 「스킬로 만들어 줘」)</t>
+          <t>다음엔 이것부터 (첫 번째 → 매번 「했어? 매뉴얼 반영했어?」까지 묻기 · 두 번째 → 어디가 왜 별로인지 짚어서 말하고 기준에 반영하기 · 세 번째 → 잘 나오면 「스킬로 만들어 줘」)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
@@ -554,7 +554,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"가 한 번 세팅이면 끝이라 생각하기,나 결과를 뭉뚱그려 말하고 탓하며 접기,다 좋은 결과를 스킬로 안 남기기"</formula1>
+      <formula1>"첫 번째 한 번 세팅이면 끝이라 생각하기,두 번째 결과를 뭉뚱그려 말하고 탓하며 접기,세 번째 좋은 결과를 스킬로 안 남기기"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -578,7 +578,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>포기하는 사람들의 공통점 가 · 나 · 다</t>
+          <t>포기하는 사람들의 공통점 세 가지</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>가. 한 번 세팅이면 끝이라 생각하기 (첫 번째)</t>
+          <t>첫 번째. 한 번 세팅이면 끝이라 생각하기</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>나. 결과를 뭉뚱그려 말하고 탓하며 접기 (두 번째)</t>
+          <t>두 번째. 결과를 뭉뚱그려 말하고 탓하며 접기</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>다. 좋은 결과를 스킬로 안 남기기 (세 번째)</t>
+          <t>세 번째. 좋은 결과를 스킬로 안 남기기</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
